--- a/stock_control/uploads/productos.xlsx
+++ b/stock_control/uploads/productos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Proyectos2024\StockControl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Proyectos2024\Gestión de Stock de Helados\stock_control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AECA8E-AF91-4FCA-BA3A-28B9EC9ADB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89932FB4-AD43-46D4-AD50-0A9BC2ED538B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C848CEC-6853-4C1E-A40D-BFA6327B2C5F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9C848CEC-6853-4C1E-A40D-BFA6327B2C5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>AMERICANA</t>
   </si>
@@ -267,6 +267,15 @@
   </si>
   <si>
     <t>PLU</t>
+  </si>
+  <si>
+    <t>CHOCO DUBAI</t>
+  </si>
+  <si>
+    <t>PISTACHO</t>
+  </si>
+  <si>
+    <t>HAVANETA LIMON</t>
   </si>
 </sst>
 </file>
@@ -638,14 +647,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5928A378-69E6-42C8-A52E-DD0AFBF7EE81}">
-  <dimension ref="A1:B76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B79"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>75</v>
       </c>
@@ -653,7 +662,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -661,7 +670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -669,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -677,7 +686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -685,7 +694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -693,7 +702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -701,7 +710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -709,7 +718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -717,7 +726,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -725,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -733,7 +742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -741,7 +750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -749,7 +758,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -757,7 +766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -765,7 +774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -773,7 +782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -781,7 +790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -789,7 +798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -797,7 +806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -805,7 +814,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -813,7 +822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -821,7 +830,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -829,7 +838,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -837,7 +846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -845,7 +854,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -853,7 +862,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -861,7 +870,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -869,7 +878,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -877,7 +886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -885,7 +894,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -893,7 +902,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -901,7 +910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -909,7 +918,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -917,7 +926,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -925,7 +934,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -933,7 +942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -941,7 +950,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -949,7 +958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -957,7 +966,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -965,7 +974,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -973,7 +982,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -981,7 +990,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -989,7 +998,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -997,7 +1006,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -1005,7 +1014,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1013,7 +1022,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1021,7 +1030,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -1029,7 +1038,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -1037,7 +1046,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -1045,7 +1054,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -1053,7 +1062,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -1061,7 +1070,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -1069,7 +1078,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -1077,7 +1086,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -1085,7 +1094,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1093,7 +1102,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1101,7 +1110,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -1109,7 +1118,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -1117,7 +1126,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -1125,7 +1134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -1133,7 +1142,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -1141,7 +1150,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -1149,107 +1158,131 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B67">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B68">
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>64</v>
       </c>
-      <c r="B66">
+      <c r="B69">
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B70">
         <v>101</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>66</v>
       </c>
-      <c r="B68">
+      <c r="B71">
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>67</v>
       </c>
-      <c r="B69">
+      <c r="B72">
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>68</v>
       </c>
-      <c r="B70">
+      <c r="B73">
         <v>104</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>69</v>
       </c>
-      <c r="B71">
+      <c r="B74">
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>70</v>
       </c>
-      <c r="B72">
+      <c r="B75">
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>71</v>
       </c>
-      <c r="B73">
+      <c r="B76">
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>72</v>
       </c>
-      <c r="B74">
+      <c r="B77">
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>73</v>
       </c>
-      <c r="B75">
+      <c r="B78">
         <v>109</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>74</v>
       </c>
-      <c r="B76">
+      <c r="B79">
         <v>110</v>
       </c>
     </row>
